--- a/POSIÇÃO DE ESTOQUE/JUNHO_2026.xlsx
+++ b/POSIÇÃO DE ESTOQUE/JUNHO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Comercial\Desktop\Dre\POSIÇÃO DE ESTOQUE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AA2CC8-8B53-435C-8530-DE576156F761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEBCBB5-26A7-43C2-830A-A5C11068345D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EF67EA2-A4F9-480E-B8AC-531488B483BD}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -87,6 +87,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -147,19 +152,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,44 +507,44 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="7">
         <v>41054</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="7">
         <v>42.158758415841582</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>677455.52529999998</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>89949</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="7">
         <v>42.125484623694632</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>1423911.3613</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="5">
         <v>131003</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="5">
         <v>42.142121519768111</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="5">
         <v>2101366.8865999999</v>
       </c>
     </row>
